--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/Moscow/ImmortalWill.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/Moscow/ImmortalWill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Specials\Moscow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B27F9507-6DC1-4E4B-A549-79FF41097CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EF492B-E6B5-4188-8847-1E5341996AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,15 +38,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HealthRegenerationMin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealthRegenerationMax</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealthRegenerationThreshold</t>
+    <t>HpRegenMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRegenMin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRegenThreshold</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -392,7 +392,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0.05</v>
@@ -400,7 +400,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0.1</v>
